--- a/lib/cumba-oss-cdisc-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-cdisc-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -157,6 +157,15 @@
   </si>
   <si>
     <t>LOINC Version</t>
+  </si>
+  <si>
+    <t>Dictionary Basis</t>
+  </si>
+  <si>
+    <t>Neoplasm Version</t>
+  </si>
+  <si>
+    <t>Library Metadata Basis</t>
   </si>
   <si>
     <t>2026-08-12T09:15:00</t>
@@ -796,7 +805,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="27.109375"/>
@@ -814,7 +823,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="8">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -822,7 +831,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -830,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s" s="8">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -854,7 +863,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s" s="8">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -868,7 +877,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s" s="8">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -884,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s" s="8">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -900,7 +909,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -908,7 +917,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -958,6 +967,26 @@
       <c r="B20" s="9" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1011,16 +1040,16 @@
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>12.5</v>
@@ -1031,16 +1060,16 @@
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>3.25</v>
@@ -1257,13 +1286,13 @@
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>2.0</v>
@@ -1271,13 +1300,13 @@
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1.0</v>
@@ -1551,87 +1580,87 @@
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F2" s="17" t="n">
         <v>3.0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F3" s="17" t="n">
         <v>9.0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F4" s="17" t="n">
         <v>1.0</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2398,58 +2427,58 @@
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3064,24 +3093,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
